--- a/ig/DM-FEVRIER-2026/ValueSet-JDV-J05-SubjectRole-CISIS.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-JDV-J05-SubjectRole-CISIS.xlsx
@@ -46,7 +46,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260202120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -73,7 +73,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T12:00:00+01:00</t>
+    <t>2026-02-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2371,7 +2371,7 @@
     <t>FON-63</t>
   </si>
   <si>
-    <t>Coordonnateur en EPHAD</t>
+    <t>Coordonnateur en EHPAD</t>
   </si>
   <si>
     <t>FON-AU</t>
